--- a/Assets/Data/Excel/RewardTable.xlsx
+++ b/Assets/Data/Excel/RewardTable.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,6 +610,53 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_003_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RWD_003</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_003_02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RWD_003</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>weapon_sword_01</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Data/Excel/RewardTable.xlsx
+++ b/Assets/Data/Excel/RewardTable.xlsx
@@ -1,45 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62581D74-2EFC-4BEF-93CA-09923D3B22FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RewardTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>rewardGroupId</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>companionId</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>itemCount</t>
+  </si>
+  <si>
+    <t>RWD_001_01</t>
+  </si>
+  <si>
+    <t>RWD_001</t>
+  </si>
+  <si>
+    <t>RWD_001_02</t>
+  </si>
+  <si>
+    <t>herb_potion</t>
+  </si>
+  <si>
+    <t>RWD_002_01</t>
+  </si>
+  <si>
+    <t>RWD_002</t>
+  </si>
+  <si>
+    <t>RWD_002_02</t>
+  </si>
+  <si>
+    <t>comp_001</t>
+  </si>
+  <si>
+    <t>RWD_002_03</t>
+  </si>
+  <si>
+    <t>iron_sword</t>
+  </si>
+  <si>
+    <t>RWD_003_01</t>
+  </si>
+  <si>
+    <t>RWD_003</t>
+  </si>
+  <si>
+    <t>RWD_003_02</t>
+  </si>
+  <si>
+    <t>comp_002</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,96 +134,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,235 +461,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rewardGroupId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>exp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>companionId</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>itemId</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>itemCount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001_01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>30</v>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>herb_potion</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
         <v>100</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>80</v>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_02</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>comp_001</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_03</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>iron_sword</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_003_01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RWD_003</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
         <v>50</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>50</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_003_02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RWD_003</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>weapon_sword_01</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/RewardTable.xlsx
+++ b/Assets/Data/Excel/RewardTable.xlsx
@@ -1,120 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\Work\UnityProject\MadHatter\Assets\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62581D74-2EFC-4BEF-93CA-09923D3B22FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RewardTable" sheetId="1" r:id="rId1"/>
+    <sheet name="RewardTable" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
-  <si>
-    <t>uniqueId</t>
-  </si>
-  <si>
-    <t>rewardGroupId</t>
-  </si>
-  <si>
-    <t>gold</t>
-  </si>
-  <si>
-    <t>exp</t>
-  </si>
-  <si>
-    <t>companionId</t>
-  </si>
-  <si>
-    <t>itemId</t>
-  </si>
-  <si>
-    <t>itemCount</t>
-  </si>
-  <si>
-    <t>RWD_001_01</t>
-  </si>
-  <si>
-    <t>RWD_001</t>
-  </si>
-  <si>
-    <t>RWD_001_02</t>
-  </si>
-  <si>
-    <t>herb_potion</t>
-  </si>
-  <si>
-    <t>RWD_002_01</t>
-  </si>
-  <si>
-    <t>RWD_002</t>
-  </si>
-  <si>
-    <t>RWD_002_02</t>
-  </si>
-  <si>
-    <t>comp_001</t>
-  </si>
-  <si>
-    <t>RWD_002_03</t>
-  </si>
-  <si>
-    <t>iron_sword</t>
-  </si>
-  <si>
-    <t>RWD_003_01</t>
-  </si>
-  <si>
-    <t>RWD_003</t>
-  </si>
-  <si>
-    <t>RWD_003_02</t>
-  </si>
-  <si>
-    <t>comp_002</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,27 +80,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,181 +447,255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>uniqueId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rewardGroupId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>companionId</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>itemId</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>itemCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RWD_001_01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RWD_001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RWD_001_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RWD_001</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>herb_potion</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002_01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002_02</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>comp_001</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002_03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>RWD_002</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>iron_sword</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_003_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RWD_003</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>50</v>
       </c>
-      <c r="D2" s="2">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_003_02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RWD_003</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>comp_002</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_004_01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RWD_004</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>80</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
+      <c r="D9" t="n">
         <v>50</v>
       </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Excel/RewardTable.xlsx
+++ b/Assets/Data/Excel/RewardTable.xlsx
@@ -6,53 +6,143 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="28800" windowHeight="15420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RewardTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RewardTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>rewardGroupId</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>companionId</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>itemCount</t>
+  </si>
+  <si>
+    <t>RWD_001_01</t>
+  </si>
+  <si>
+    <t>RWD_001</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>RWD_001_02</t>
+  </si>
+  <si>
+    <t>potion_hp_small</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RWD_002_01</t>
+  </si>
+  <si>
+    <t>RWD_002</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>RWD_002_02</t>
+  </si>
+  <si>
+    <t>comp_001</t>
+  </si>
+  <si>
+    <t>RWD_003_01</t>
+  </si>
+  <si>
+    <t>RWD_003</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>RWD_004_01</t>
+  </si>
+  <si>
+    <t>RWD_004</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>RWD_004_02</t>
+  </si>
+  <si>
+    <t>comp_002</t>
+  </si>
+  <si>
+    <t>RWD_005_01</t>
+  </si>
+  <si>
+    <t>RWD_005</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,33 +150,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -454,248 +524,216 @@
   </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>uniqueId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rewardGroupId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>exp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>companionId</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>itemId</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>itemCount</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001_01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RWD_001</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>herb_potion</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_02</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>comp_001</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002_03</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>RWD_002</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>iron_sword</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_003_01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RWD_003</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_003_02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RWD_003</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>comp_002</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_004_01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RWD_004</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>80</v>
-      </c>
-      <c r="D9" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>